--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/46.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/46.xlsx
@@ -426,13 +426,13 @@
         <v>-8.179421708420836</v>
       </c>
       <c r="E2">
-        <v>-4.678554241466163</v>
+        <v>-8.082458713389718</v>
       </c>
       <c r="F2">
-        <v>-2.68818159464674</v>
+        <v>-3.55270309274143</v>
       </c>
       <c r="G2">
-        <v>-5.429087270704106</v>
+        <v>-4.637310715167695</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.136145678505034</v>
       </c>
       <c r="E3">
-        <v>-5.800076114205804</v>
+        <v>-9.141243107227092</v>
       </c>
       <c r="F3">
-        <v>-2.754708609132971</v>
+        <v>-3.391408362272727</v>
       </c>
       <c r="G3">
-        <v>-5.072260119753762</v>
+        <v>-4.819092770729076</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.096191859991489</v>
       </c>
       <c r="E4">
-        <v>-7.021396497126483</v>
+        <v>-9.042943521942593</v>
       </c>
       <c r="F4">
-        <v>-2.56372104911092</v>
+        <v>-3.56209180888476</v>
       </c>
       <c r="G4">
-        <v>-4.298343957401719</v>
+        <v>-4.776651576915619</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.216805137891143</v>
       </c>
       <c r="E5">
-        <v>-7.686579515639175</v>
+        <v>-9.780731564220263</v>
       </c>
       <c r="F5">
-        <v>-2.643107639158211</v>
+        <v>-3.628956797271333</v>
       </c>
       <c r="G5">
-        <v>-4.47108491309535</v>
+        <v>-4.572496854599844</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.481713861222365</v>
       </c>
       <c r="E6">
-        <v>-8.281294950118507</v>
+        <v>-10.70610258531766</v>
       </c>
       <c r="F6">
-        <v>-2.918601099776854</v>
+        <v>-3.557596258989767</v>
       </c>
       <c r="G6">
-        <v>-3.571950676265913</v>
+        <v>-4.254512334461768</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.921886010686844</v>
       </c>
       <c r="E7">
-        <v>-9.158682260630631</v>
+        <v>-11.73066530107907</v>
       </c>
       <c r="F7">
-        <v>-2.936038233605783</v>
+        <v>-4.104418148925776</v>
       </c>
       <c r="G7">
-        <v>-3.528609014065775</v>
+        <v>-4.286085007269797</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.528724028449742</v>
       </c>
       <c r="E8">
-        <v>-10.23136454119755</v>
+        <v>-12.08230583624868</v>
       </c>
       <c r="F8">
-        <v>-2.935813746039624</v>
+        <v>-3.889384739935261</v>
       </c>
       <c r="G8">
-        <v>-3.436608953529428</v>
+        <v>-3.491368687294513</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.298100959879974</v>
       </c>
       <c r="E9">
-        <v>-10.95051338445965</v>
+        <v>-12.38698609595875</v>
       </c>
       <c r="F9">
-        <v>-2.931250270017602</v>
+        <v>-3.542236670607058</v>
       </c>
       <c r="G9">
-        <v>-2.972321494374341</v>
+        <v>-3.489998121441255</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.209232431603676</v>
       </c>
       <c r="E10">
-        <v>-11.67581642389817</v>
+        <v>-13.36661276414205</v>
       </c>
       <c r="F10">
-        <v>-2.956565177847155</v>
+        <v>-3.927686791905905</v>
       </c>
       <c r="G10">
-        <v>-2.144863879015665</v>
+        <v>-3.104150728293659</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.234171257822578</v>
       </c>
       <c r="E11">
-        <v>-11.54945388518814</v>
+        <v>-13.99821714788787</v>
       </c>
       <c r="F11">
-        <v>-2.928531568201614</v>
+        <v>-3.759787488134681</v>
       </c>
       <c r="G11">
-        <v>-1.653267729707129</v>
+        <v>-2.791913315211758</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.3452111178613</v>
       </c>
       <c r="E12">
-        <v>-12.94550090922077</v>
+        <v>-14.35736589296219</v>
       </c>
       <c r="F12">
-        <v>-2.908924940144753</v>
+        <v>-3.917375274475857</v>
       </c>
       <c r="G12">
-        <v>-1.37454296911927</v>
+        <v>-2.20580109075703</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.502203562682341</v>
       </c>
       <c r="E13">
-        <v>-14.03600726348187</v>
+        <v>-15.35335393773521</v>
       </c>
       <c r="F13">
-        <v>-2.813369446762218</v>
+        <v>-3.599935773681655</v>
       </c>
       <c r="G13">
-        <v>-1.198680168982106</v>
+        <v>-1.830742765521918</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.678701654993427</v>
       </c>
       <c r="E14">
-        <v>-14.87628825797515</v>
+        <v>-15.59882439979499</v>
       </c>
       <c r="F14">
-        <v>-2.955624980844977</v>
+        <v>-3.571803588315181</v>
       </c>
       <c r="G14">
-        <v>-0.9862126668172205</v>
+        <v>-1.167945064195512</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.839570700402508</v>
       </c>
       <c r="E15">
-        <v>-15.51431854633785</v>
+        <v>-16.33197981316281</v>
       </c>
       <c r="F15">
-        <v>-2.535352779034648</v>
+        <v>-3.350488669309237</v>
       </c>
       <c r="G15">
-        <v>0.05759241007836693</v>
+        <v>-0.8369335473604042</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.969579723272624</v>
       </c>
       <c r="E16">
-        <v>-16.20477950676135</v>
+        <v>-17.73790343900617</v>
       </c>
       <c r="F16">
-        <v>-2.532304386992346</v>
+        <v>-3.284785880388792</v>
       </c>
       <c r="G16">
-        <v>0.3435838181249262</v>
+        <v>-0.4932492622009659</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.055075653531783</v>
       </c>
       <c r="E17">
-        <v>-16.71445019937664</v>
+        <v>-19.17856046048836</v>
       </c>
       <c r="F17">
-        <v>-2.195717173682434</v>
+        <v>-3.138192186217572</v>
       </c>
       <c r="G17">
-        <v>0.3808406976238842</v>
+        <v>-0.8737468137570997</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.100981200953621</v>
       </c>
       <c r="E18">
-        <v>-17.74418443245481</v>
+        <v>-18.82454247646472</v>
       </c>
       <c r="F18">
-        <v>-1.907941509582483</v>
+        <v>-2.782355371201405</v>
       </c>
       <c r="G18">
-        <v>1.023593045710003</v>
+        <v>-0.2292167027163924</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.116235778870023</v>
       </c>
       <c r="E19">
-        <v>-18.92230770181632</v>
+        <v>-20.32669617497108</v>
       </c>
       <c r="F19">
-        <v>-1.37430391522943</v>
+        <v>-2.156223101019162</v>
       </c>
       <c r="G19">
-        <v>1.517943568907212</v>
+        <v>0.539134432584136</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.118180788962265</v>
       </c>
       <c r="E20">
-        <v>-19.39591362743452</v>
+        <v>-21.10856438323941</v>
       </c>
       <c r="F20">
-        <v>-1.455902246242196</v>
+        <v>-2.252490990368104</v>
       </c>
       <c r="G20">
-        <v>1.154356283965676</v>
+        <v>-0.0904386337101442</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.125033532676126</v>
       </c>
       <c r="E21">
-        <v>-20.6337674689572</v>
+        <v>-21.33778215208567</v>
       </c>
       <c r="F21">
-        <v>-1.003932565763743</v>
+        <v>-1.770841734214748</v>
       </c>
       <c r="G21">
-        <v>1.062773352167278</v>
+        <v>-0.235377627964976</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.152771515867395</v>
       </c>
       <c r="E22">
-        <v>-20.71239989162639</v>
+        <v>-21.69564028206781</v>
       </c>
       <c r="F22">
-        <v>-0.2116165407014751</v>
+        <v>-1.277504214007891</v>
       </c>
       <c r="G22">
-        <v>0.8827624384694066</v>
+        <v>-0.1313371133023004</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.217134291450031</v>
       </c>
       <c r="E23">
-        <v>-20.74250065835538</v>
+        <v>-22.59675226790612</v>
       </c>
       <c r="F23">
-        <v>-0.1785820770452336</v>
+        <v>-1.167194668814095</v>
       </c>
       <c r="G23">
-        <v>0.5358470608636396</v>
+        <v>-0.4997842790954872</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.32155707627494</v>
       </c>
       <c r="E24">
-        <v>-21.38112417681308</v>
+        <v>-22.81960753077159</v>
       </c>
       <c r="F24">
-        <v>0.09919767760513584</v>
+        <v>-0.7282253863551783</v>
       </c>
       <c r="G24">
-        <v>-0.3391334357112743</v>
+        <v>-1.140407946399855</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.470460998193174</v>
       </c>
       <c r="E25">
-        <v>-22.00581358074918</v>
+        <v>-23.02724712097129</v>
       </c>
       <c r="F25">
-        <v>-0.008190215758986465</v>
+        <v>-0.7863303894571468</v>
       </c>
       <c r="G25">
-        <v>-0.1278180033940552</v>
+        <v>-1.527245192663693</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.652180714685366</v>
       </c>
       <c r="E26">
-        <v>-21.7423379060349</v>
+        <v>-23.17853438061955</v>
       </c>
       <c r="F26">
-        <v>0.03771045039753694</v>
+        <v>-0.7776863756089341</v>
       </c>
       <c r="G26">
-        <v>-0.5965117986619127</v>
+        <v>-1.269287484243682</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.859507155242518</v>
       </c>
       <c r="E27">
-        <v>-21.80077333462988</v>
+        <v>-24.10970184844676</v>
       </c>
       <c r="F27">
-        <v>0.3694202364397653</v>
+        <v>-0.5430587640725992</v>
       </c>
       <c r="G27">
-        <v>-1.605946791768787</v>
+        <v>-1.924447757010989</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.071869600495998</v>
       </c>
       <c r="E28">
-        <v>-22.05500639389451</v>
+        <v>-22.47599145154357</v>
       </c>
       <c r="F28">
-        <v>0.4830407661425511</v>
+        <v>-0.2994475080529038</v>
       </c>
       <c r="G28">
-        <v>-1.655250746485152</v>
+        <v>-2.34574778233864</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.272300913478875</v>
       </c>
       <c r="E29">
-        <v>-21.76828606209886</v>
+        <v>-22.17893261358841</v>
       </c>
       <c r="F29">
-        <v>0.5506893900921728</v>
+        <v>-0.6509121999170949</v>
       </c>
       <c r="G29">
-        <v>-1.727175658871358</v>
+        <v>-2.702306779100304</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.43810354681542</v>
       </c>
       <c r="E30">
-        <v>-21.19601374480154</v>
+        <v>-22.68311932418041</v>
       </c>
       <c r="F30">
-        <v>0.6542502260553614</v>
+        <v>-0.6334270207788029</v>
       </c>
       <c r="G30">
-        <v>-2.165819632279252</v>
+        <v>-2.692130162112585</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.54869927689231</v>
       </c>
       <c r="E31">
-        <v>-20.84017531422682</v>
+        <v>-21.95647585643561</v>
       </c>
       <c r="F31">
-        <v>0.5868741349812608</v>
+        <v>-0.3215665744424562</v>
       </c>
       <c r="G31">
-        <v>-2.19934883750099</v>
+        <v>-2.786911080901919</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.585959746983375</v>
       </c>
       <c r="E32">
-        <v>-20.34590596171162</v>
+        <v>-22.00822272892126</v>
       </c>
       <c r="F32">
-        <v>0.4322063437349539</v>
+        <v>-0.7362315573032355</v>
       </c>
       <c r="G32">
-        <v>-2.334276742045066</v>
+        <v>-2.764955542885472</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.534460328751456</v>
       </c>
       <c r="E33">
-        <v>-20.21091215154297</v>
+        <v>-21.93415953652582</v>
       </c>
       <c r="F33">
-        <v>0.2067263934277341</v>
+        <v>-0.6075728457700276</v>
       </c>
       <c r="G33">
-        <v>-2.269171553469759</v>
+        <v>-2.995395996783061</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.391061511775815</v>
       </c>
       <c r="E34">
-        <v>-20.11964528639238</v>
+        <v>-21.84253039345461</v>
       </c>
       <c r="F34">
-        <v>0.3557612863350043</v>
+        <v>-0.5617956063565213</v>
       </c>
       <c r="G34">
-        <v>-1.934902459824007</v>
+        <v>-3.111308127749563</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.155517425073652</v>
       </c>
       <c r="E35">
-        <v>-19.58394945365501</v>
+        <v>-21.67145823086685</v>
       </c>
       <c r="F35">
-        <v>0.5385455239671321</v>
+        <v>-0.7111684731641337</v>
       </c>
       <c r="G35">
-        <v>-2.394803446139561</v>
+        <v>-2.646835278044276</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.8434822950382</v>
       </c>
       <c r="E36">
-        <v>-19.00532821579894</v>
+        <v>-21.22076185525346</v>
       </c>
       <c r="F36">
-        <v>0.3066589801666608</v>
+        <v>-0.8821567589803965</v>
       </c>
       <c r="G36">
-        <v>-2.316840098689724</v>
+        <v>-2.847600001727838</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.469392912070164</v>
       </c>
       <c r="E37">
-        <v>-18.10374526866384</v>
+        <v>-20.05773198975951</v>
       </c>
       <c r="F37">
-        <v>0.138873162729621</v>
+        <v>-0.7986614666152203</v>
       </c>
       <c r="G37">
-        <v>-1.993747406784553</v>
+        <v>-2.384517581149045</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.058947071644107</v>
       </c>
       <c r="E38">
-        <v>-18.77012833278856</v>
+        <v>-19.88596697064857</v>
       </c>
       <c r="F38">
-        <v>-0.06805549959190393</v>
+        <v>-0.6168033437394225</v>
       </c>
       <c r="G38">
-        <v>-2.526692269878586</v>
+        <v>-2.019268402346794</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.634838716592815</v>
       </c>
       <c r="E39">
-        <v>-17.73268663694933</v>
+        <v>-19.50648990575381</v>
       </c>
       <c r="F39">
-        <v>-0.1994950404963099</v>
+        <v>-1.058308258818309</v>
       </c>
       <c r="G39">
-        <v>-1.148724036794504</v>
+        <v>-1.846203013190315</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.225075033602829</v>
       </c>
       <c r="E40">
-        <v>-16.28262397495321</v>
+        <v>-18.56561791812816</v>
       </c>
       <c r="F40">
-        <v>-0.1360437541766734</v>
+        <v>-0.9687335780839867</v>
       </c>
       <c r="G40">
-        <v>-1.538156750761131</v>
+        <v>-1.673882496780171</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.853560381796016</v>
       </c>
       <c r="E41">
-        <v>-17.17399974167503</v>
+        <v>-18.30077917273757</v>
       </c>
       <c r="F41">
-        <v>-0.1874273841723267</v>
+        <v>-1.239255177551027</v>
       </c>
       <c r="G41">
-        <v>-1.277560537546321</v>
+        <v>-1.690074375012746</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.541252826064595</v>
       </c>
       <c r="E42">
-        <v>-16.17313453039575</v>
+        <v>-18.52905049051622</v>
       </c>
       <c r="F42">
-        <v>-0.4481709348167215</v>
+        <v>-1.398006820093135</v>
       </c>
       <c r="G42">
-        <v>-0.8606436745126644</v>
+        <v>-1.325838223145512</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.30537522844344</v>
       </c>
       <c r="E43">
-        <v>-15.63985690277848</v>
+        <v>-17.3775501198458</v>
       </c>
       <c r="F43">
-        <v>-0.6607498911927419</v>
+        <v>-1.325266221718505</v>
       </c>
       <c r="G43">
-        <v>-1.481357720943855</v>
+        <v>-1.335031608108068</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.152339464380387</v>
       </c>
       <c r="E44">
-        <v>-16.54120436926519</v>
+        <v>-17.34432923452553</v>
       </c>
       <c r="F44">
-        <v>-0.4629498376500675</v>
+        <v>-1.386830487094564</v>
       </c>
       <c r="G44">
-        <v>-0.7370709411682889</v>
+        <v>-0.3762347195698865</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.086182668039596</v>
       </c>
       <c r="E45">
-        <v>-14.19717112494085</v>
+        <v>-16.16167296268234</v>
       </c>
       <c r="F45">
-        <v>-0.7729953310068804</v>
+        <v>-1.221090737142439</v>
       </c>
       <c r="G45">
-        <v>-0.7627773272807296</v>
+        <v>-0.8071949167811311</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.095813795719604</v>
       </c>
       <c r="E46">
-        <v>-14.72890907139552</v>
+        <v>-16.35564561832689</v>
       </c>
       <c r="F46">
-        <v>-0.9433838788235164</v>
+        <v>-1.59324141978934</v>
       </c>
       <c r="G46">
-        <v>-1.129853927220658</v>
+        <v>-1.199564084641092</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.173457288123863</v>
       </c>
       <c r="E47">
-        <v>-14.04809376060835</v>
+        <v>-15.68796741063598</v>
       </c>
       <c r="F47">
-        <v>-0.7038051153206489</v>
+        <v>-1.638039528932737</v>
       </c>
       <c r="G47">
-        <v>-0.5527397655416691</v>
+        <v>-1.012389150396238</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.29825714379908</v>
       </c>
       <c r="E48">
-        <v>-12.82224490368</v>
+        <v>-15.7732929178885</v>
       </c>
       <c r="F48">
-        <v>-0.9856297879988883</v>
+        <v>-1.422712049514228</v>
       </c>
       <c r="G48">
-        <v>-0.5597912275403167</v>
+        <v>-1.195651019813673</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.45877192230443</v>
       </c>
       <c r="E49">
-        <v>-13.30328205514478</v>
+        <v>-14.87127976572267</v>
       </c>
       <c r="F49">
-        <v>-1.045660745312366</v>
+        <v>-1.710592916274335</v>
       </c>
       <c r="G49">
-        <v>-0.9596521599556478</v>
+        <v>-0.5358162567449148</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.637771234952948</v>
       </c>
       <c r="E50">
-        <v>-12.50779219706138</v>
+        <v>-14.11381550388167</v>
       </c>
       <c r="F50">
-        <v>-1.067309299017128</v>
+        <v>-1.810732594863961</v>
       </c>
       <c r="G50">
-        <v>-1.164386227740796</v>
+        <v>-0.9467807588989614</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.830300957946535</v>
       </c>
       <c r="E51">
-        <v>-12.14679130611791</v>
+        <v>-14.02460456593056</v>
       </c>
       <c r="F51">
-        <v>-0.9248533000228913</v>
+        <v>-1.574013355635558</v>
       </c>
       <c r="G51">
-        <v>-0.5532197946448635</v>
+        <v>-1.561502717904071</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.028507493807814</v>
       </c>
       <c r="E52">
-        <v>-11.66396087894609</v>
+        <v>-13.2849326784657</v>
       </c>
       <c r="F52">
-        <v>-0.9730808502138786</v>
+        <v>-2.006280317438423</v>
       </c>
       <c r="G52">
-        <v>-1.214610514117079</v>
+        <v>-1.419443898268405</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.232033325839222</v>
       </c>
       <c r="E53">
-        <v>-11.50805910428402</v>
+        <v>-13.31568554545179</v>
       </c>
       <c r="F53">
-        <v>-1.193640298148469</v>
+        <v>-1.668357775875199</v>
       </c>
       <c r="G53">
-        <v>-1.084383584238768</v>
+        <v>-1.420307950654155</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.439763453113893</v>
       </c>
       <c r="E54">
-        <v>-10.34001621806358</v>
+        <v>-12.5840879271426</v>
       </c>
       <c r="F54">
-        <v>-1.435130933616998</v>
+        <v>-1.5904779861336</v>
       </c>
       <c r="G54">
-        <v>-1.509371557297168</v>
+        <v>-1.806628751813867</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.651942478507275</v>
       </c>
       <c r="E55">
-        <v>-10.89210512670871</v>
+        <v>-11.68721912144948</v>
       </c>
       <c r="F55">
-        <v>-1.287500951824876</v>
+        <v>-1.801607299554722</v>
       </c>
       <c r="G55">
-        <v>-1.56178080372937</v>
+        <v>-1.717522108078844</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.868697014181568</v>
       </c>
       <c r="E56">
-        <v>-9.58252025690453</v>
+        <v>-11.78669610997598</v>
       </c>
       <c r="F56">
-        <v>-1.298203458669045</v>
+        <v>-1.895564872217256</v>
       </c>
       <c r="G56">
-        <v>-1.758221954938644</v>
+        <v>-1.67043290832825</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.086664330319635</v>
       </c>
       <c r="E57">
-        <v>-9.242481672142571</v>
+        <v>-11.38664618766437</v>
       </c>
       <c r="F57">
-        <v>-1.432384067309315</v>
+        <v>-1.944142821819627</v>
       </c>
       <c r="G57">
-        <v>-2.409353293784658</v>
+        <v>-2.19539935667264</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.306192203729968</v>
       </c>
       <c r="E58">
-        <v>-8.791441132504596</v>
+        <v>-11.28380907142418</v>
       </c>
       <c r="F58">
-        <v>-1.079399321260987</v>
+        <v>-1.795500575061284</v>
       </c>
       <c r="G58">
-        <v>-1.986930993519193</v>
+        <v>-2.83714529891482</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.518755273643185</v>
       </c>
       <c r="E59">
-        <v>-9.152278998383785</v>
+        <v>-10.74848910202946</v>
       </c>
       <c r="F59">
-        <v>-1.454902406787017</v>
+        <v>-1.815442691916279</v>
       </c>
       <c r="G59">
-        <v>-2.725374660417946</v>
+        <v>-2.310026995969904</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.721131049268247</v>
       </c>
       <c r="E60">
-        <v>-8.829643339233304</v>
+        <v>-11.13012624902588</v>
       </c>
       <c r="F60">
-        <v>-1.50163144034634</v>
+        <v>-1.976157565203022</v>
       </c>
       <c r="G60">
-        <v>-2.471452507010307</v>
+        <v>-2.944870450762704</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.899575160436135</v>
       </c>
       <c r="E61">
-        <v>-8.51958778087613</v>
+        <v>-10.64910268298311</v>
       </c>
       <c r="F61">
-        <v>-1.399856564503587</v>
+        <v>-1.609118737798798</v>
       </c>
       <c r="G61">
-        <v>-3.118468837751007</v>
+        <v>-3.122659988403724</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.048978345235134</v>
       </c>
       <c r="E62">
-        <v>-7.062247861149678</v>
+        <v>-10.55414511151628</v>
       </c>
       <c r="F62">
-        <v>-1.608177712429218</v>
+        <v>-1.801320684433353</v>
       </c>
       <c r="G62">
-        <v>-3.140997100145747</v>
+        <v>-3.186219152212192</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.159834956087762</v>
       </c>
       <c r="E63">
-        <v>-7.694454531938513</v>
+        <v>-9.839388888041617</v>
       </c>
       <c r="F63">
-        <v>-1.458153748843005</v>
+        <v>-1.888754035431438</v>
       </c>
       <c r="G63">
-        <v>-3.301975687538348</v>
+        <v>-2.817570043141109</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.231291423235213</v>
       </c>
       <c r="E64">
-        <v>-7.14118369157738</v>
+        <v>-9.764370187630549</v>
       </c>
       <c r="F64">
-        <v>-1.740334619504448</v>
+        <v>-1.86568648836568</v>
       </c>
       <c r="G64">
-        <v>-3.661603560014916</v>
+        <v>-3.329512805334006</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.263828707713675</v>
       </c>
       <c r="E65">
-        <v>-6.820726228424587</v>
+        <v>-9.198895109818745</v>
       </c>
       <c r="F65">
-        <v>-1.58892728235556</v>
+        <v>-1.930650373562829</v>
       </c>
       <c r="G65">
-        <v>-3.424624778677267</v>
+        <v>-3.409502206653876</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.262765744210049</v>
       </c>
       <c r="E66">
-        <v>-7.555335281948873</v>
+        <v>-8.522879981479706</v>
       </c>
       <c r="F66">
-        <v>-1.506919737845812</v>
+        <v>-1.842645449056812</v>
       </c>
       <c r="G66">
-        <v>-3.839254054743287</v>
+        <v>-3.326569730349593</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.239068373265747</v>
       </c>
       <c r="E67">
-        <v>-6.995217388888141</v>
+        <v>-9.531298687403771</v>
       </c>
       <c r="F67">
-        <v>-1.87499236776873</v>
+        <v>-2.002109487565328</v>
       </c>
       <c r="G67">
-        <v>-3.298946538369915</v>
+        <v>-3.442670562411834</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.200583584524754</v>
       </c>
       <c r="E68">
-        <v>-7.007457854130874</v>
+        <v>-9.273076042538392</v>
       </c>
       <c r="F68">
-        <v>-2.085292485419649</v>
+        <v>-2.077157089156755</v>
       </c>
       <c r="G68">
-        <v>-4.048351421549194</v>
+        <v>-3.731287233071035</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.161192758594908</v>
       </c>
       <c r="E69">
-        <v>-7.550806807941202</v>
+        <v>-8.943711071012512</v>
       </c>
       <c r="F69">
-        <v>-2.194452256658359</v>
+        <v>-2.143105074828429</v>
       </c>
       <c r="G69">
-        <v>-3.918885917144916</v>
+        <v>-3.987695606178667</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.123890960296904</v>
       </c>
       <c r="E70">
-        <v>-7.351947928842374</v>
+        <v>-9.1747221155658</v>
       </c>
       <c r="F70">
-        <v>-2.171059161203301</v>
+        <v>-2.51617027508802</v>
       </c>
       <c r="G70">
-        <v>-3.484539031846997</v>
+        <v>-4.297009807549392</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.099055552381899</v>
       </c>
       <c r="E71">
-        <v>-7.029579449658343</v>
+        <v>-8.969577714544325</v>
       </c>
       <c r="F71">
-        <v>-2.179728854441001</v>
+        <v>-2.413391417953074</v>
       </c>
       <c r="G71">
-        <v>-3.340874597624784</v>
+        <v>-3.908653020883028</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.083653495704061</v>
       </c>
       <c r="E72">
-        <v>-6.703017603543211</v>
+        <v>-8.816438309026937</v>
       </c>
       <c r="F72">
-        <v>-2.206190222756028</v>
+        <v>-2.379378652394127</v>
       </c>
       <c r="G72">
-        <v>-3.450106047693037</v>
+        <v>-4.172169135263475</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.079886165239718</v>
       </c>
       <c r="E73">
-        <v>-6.843893901447829</v>
+        <v>-9.51075300083097</v>
       </c>
       <c r="F73">
-        <v>-2.159469472870733</v>
+        <v>-2.132038086327028</v>
       </c>
       <c r="G73">
-        <v>-3.808273969586787</v>
+        <v>-3.608644763023195</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.079561973971085</v>
       </c>
       <c r="E74">
-        <v>-7.159370043192184</v>
+        <v>-9.6207586914253</v>
       </c>
       <c r="F74">
-        <v>-2.237812319990497</v>
+        <v>-2.407705504100258</v>
       </c>
       <c r="G74">
-        <v>-3.214448174025557</v>
+        <v>-3.773112665414188</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.076289347663184</v>
       </c>
       <c r="E75">
-        <v>-7.745146269980375</v>
+        <v>-9.179345687527631</v>
       </c>
       <c r="F75">
-        <v>-2.108626766789108</v>
+        <v>-2.442935969741321</v>
       </c>
       <c r="G75">
-        <v>-2.780809745473042</v>
+        <v>-3.756076598069098</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.061095836943896</v>
       </c>
       <c r="E76">
-        <v>-8.160751500508329</v>
+        <v>-10.65540631880179</v>
       </c>
       <c r="F76">
-        <v>-2.229607340865767</v>
+        <v>-2.443136434652799</v>
       </c>
       <c r="G76">
-        <v>-2.658723447075799</v>
+        <v>-3.508497449914702</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.024973952102025</v>
       </c>
       <c r="E77">
-        <v>-7.807557698754088</v>
+        <v>-10.51409075891843</v>
       </c>
       <c r="F77">
-        <v>-2.350455376157979</v>
+        <v>-2.802134299678049</v>
       </c>
       <c r="G77">
-        <v>-1.802675960439977</v>
+        <v>-3.617123070149268</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.96490043068802</v>
       </c>
       <c r="E78">
-        <v>-9.150358925404534</v>
+        <v>-10.24947390875422</v>
       </c>
       <c r="F78">
-        <v>-2.464215899951838</v>
+        <v>-2.732183642716047</v>
       </c>
       <c r="G78">
-        <v>-2.210283569417203</v>
+        <v>-3.004768151204738</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.87508347331006</v>
       </c>
       <c r="E79">
-        <v>-9.311246549949045</v>
+        <v>-10.65489912971293</v>
       </c>
       <c r="F79">
-        <v>-2.342261994176889</v>
+        <v>-3.008882377905763</v>
       </c>
       <c r="G79">
-        <v>-2.341563252777001</v>
+        <v>-2.926427401563424</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.760763924368828</v>
       </c>
       <c r="E80">
-        <v>-9.469100096908418</v>
+        <v>-11.92993174283859</v>
       </c>
       <c r="F80">
-        <v>-2.793749564826912</v>
+        <v>-3.228533935166886</v>
       </c>
       <c r="G80">
-        <v>-2.18526577677693</v>
+        <v>-2.70155528526289</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.62120525525398</v>
       </c>
       <c r="E81">
-        <v>-10.87334365889494</v>
+        <v>-12.51189952298633</v>
       </c>
       <c r="F81">
-        <v>-3.03013580035939</v>
+        <v>-3.218399688361036</v>
       </c>
       <c r="G81">
-        <v>-2.08678697862023</v>
+        <v>-2.850178916702931</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.468959901499268</v>
       </c>
       <c r="E82">
-        <v>-11.52555259937565</v>
+        <v>-12.89804703009439</v>
       </c>
       <c r="F82">
-        <v>-3.005876232601004</v>
+        <v>-2.731330424291164</v>
       </c>
       <c r="G82">
-        <v>-1.215885074149698</v>
+        <v>-3.051218415666252</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.309524892253622</v>
       </c>
       <c r="E83">
-        <v>-12.10825852078664</v>
+        <v>-14.26120827588332</v>
       </c>
       <c r="F83">
-        <v>-3.097221962842511</v>
+        <v>-3.328776331314459</v>
       </c>
       <c r="G83">
-        <v>-1.707355422727742</v>
+        <v>-2.423211237412047</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.158219557216711</v>
       </c>
       <c r="E84">
-        <v>-13.26945435430748</v>
+        <v>-14.82051557209668</v>
       </c>
       <c r="F84">
-        <v>-3.095139447191873</v>
+        <v>-3.479239329624156</v>
       </c>
       <c r="G84">
-        <v>-0.6639774062067203</v>
+        <v>-2.332343383450131</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.022791043679137</v>
       </c>
       <c r="E85">
-        <v>-13.77155796685595</v>
+        <v>-16.02410697927733</v>
       </c>
       <c r="F85">
-        <v>-3.614708877943182</v>
+        <v>-3.494155741446367</v>
       </c>
       <c r="G85">
-        <v>-1.262593561163275</v>
+        <v>-2.821843957432308</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.913360227599209</v>
       </c>
       <c r="E86">
-        <v>-15.59017501444033</v>
+        <v>-17.44854753533806</v>
       </c>
       <c r="F86">
-        <v>-3.757401790014619</v>
+        <v>-3.518933867198906</v>
       </c>
       <c r="G86">
-        <v>-1.110616347091953</v>
+        <v>-1.836787821676627</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.8343797476742</v>
       </c>
       <c r="E87">
-        <v>-16.82068819959659</v>
+        <v>-17.92586228116853</v>
       </c>
       <c r="F87">
-        <v>-3.751623927380092</v>
+        <v>-3.533349116742423</v>
       </c>
       <c r="G87">
-        <v>-0.5198826010644025</v>
+        <v>-2.332965766011514</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.787422119944793</v>
       </c>
       <c r="E88">
-        <v>-17.42391716521034</v>
+        <v>-19.78582882491696</v>
       </c>
       <c r="F88">
-        <v>-3.78031360400865</v>
+        <v>-3.871121723805741</v>
       </c>
       <c r="G88">
-        <v>-0.7857558238688109</v>
+        <v>-2.105153885272107</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.774635032887912</v>
       </c>
       <c r="E89">
-        <v>-20.09548587756146</v>
+        <v>-20.98646766704461</v>
       </c>
       <c r="F89">
-        <v>-3.753433081787807</v>
+        <v>-3.892776904449725</v>
       </c>
       <c r="G89">
-        <v>-0.6189109497806216</v>
+        <v>-2.226478758195317</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.791995573420967</v>
       </c>
       <c r="E90">
-        <v>-20.8649596524708</v>
+        <v>-23.2847769093135</v>
       </c>
       <c r="F90">
-        <v>-3.947918008984477</v>
+        <v>-4.262479761421353</v>
       </c>
       <c r="G90">
-        <v>-0.8150111147993504</v>
+        <v>-1.595369598770815</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.842023057883126</v>
       </c>
       <c r="E91">
-        <v>-23.47878579275011</v>
+        <v>-24.99283579247462</v>
       </c>
       <c r="F91">
-        <v>-4.222131641965794</v>
+        <v>-4.47864389191669</v>
       </c>
       <c r="G91">
-        <v>-1.62123820161468</v>
+        <v>-2.271022148426211</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.917498186182622</v>
       </c>
       <c r="E92">
-        <v>-24.19247329635896</v>
+        <v>-26.76439293817129</v>
       </c>
       <c r="F92">
-        <v>-4.447359768582563</v>
+        <v>-4.809757253428902</v>
       </c>
       <c r="G92">
-        <v>-1.065576375030169</v>
+        <v>-2.377141685687549</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.022760541676935</v>
       </c>
       <c r="E93">
-        <v>-26.82523751493835</v>
+        <v>-28.0696802861422</v>
       </c>
       <c r="F93">
-        <v>-4.3108431638664</v>
+        <v>-4.727838344231253</v>
       </c>
       <c r="G93">
-        <v>-1.632659583725166</v>
+        <v>-2.560410176196063</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.150465234283051</v>
       </c>
       <c r="E94">
-        <v>-28.44968265402185</v>
+        <v>-30.45245915407616</v>
       </c>
       <c r="F94">
-        <v>-4.377281543040531</v>
+        <v>-4.82206016609528</v>
       </c>
       <c r="G94">
-        <v>-1.99344283659494</v>
+        <v>-2.818626107168137</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.3039479728196</v>
       </c>
       <c r="E95">
-        <v>-30.51277389938432</v>
+        <v>-33.09046734555644</v>
       </c>
       <c r="F95">
-        <v>-4.891598296090688</v>
+        <v>-4.943785442467057</v>
       </c>
       <c r="G95">
-        <v>-2.686618103789698</v>
+        <v>-3.168395175028755</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.481464181502392</v>
       </c>
       <c r="E96">
-        <v>-33.73005995745179</v>
+        <v>-34.86385625898922</v>
       </c>
       <c r="F96">
-        <v>-4.714163655145839</v>
+        <v>-5.035780612752359</v>
       </c>
       <c r="G96">
-        <v>-2.965657366203788</v>
+        <v>-3.511486872536664</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.681355588636886</v>
       </c>
       <c r="E97">
-        <v>-35.99376486559106</v>
+        <v>-37.44986624767642</v>
       </c>
       <c r="F97">
-        <v>-4.953065642480619</v>
+        <v>-5.350676197252563</v>
       </c>
       <c r="G97">
-        <v>-3.199895015834921</v>
+        <v>-3.171450808561503</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.913443402865504</v>
       </c>
       <c r="E98">
-        <v>-37.91977467426735</v>
+        <v>-40.07133871631768</v>
       </c>
       <c r="F98">
-        <v>-5.053021423506824</v>
+        <v>-5.236303509948035</v>
       </c>
       <c r="G98">
-        <v>-3.443150591515028</v>
+        <v>-3.772198954845349</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.165679765315813</v>
       </c>
       <c r="E99">
-        <v>-41.15401986749353</v>
+        <v>-42.66558599922483</v>
       </c>
       <c r="F99">
-        <v>-5.275898643434449</v>
+        <v>-5.546380481266154</v>
       </c>
       <c r="G99">
-        <v>-3.89683768385337</v>
+        <v>-4.759529435386509</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.466779029109224</v>
       </c>
       <c r="E100">
-        <v>-43.4902754577097</v>
+        <v>-44.89223666879635</v>
       </c>
       <c r="F100">
-        <v>-5.256884298070589</v>
+        <v>-5.576225730421617</v>
       </c>
       <c r="G100">
-        <v>-4.831437795045018</v>
+        <v>-5.075328995468666</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.779157981044994</v>
       </c>
       <c r="E101">
-        <v>-46.09248153368533</v>
+        <v>-47.58898369663012</v>
       </c>
       <c r="F101">
-        <v>-5.376588357979534</v>
+        <v>-5.679214992876875</v>
       </c>
       <c r="G101">
-        <v>-5.228296062656231</v>
+        <v>-5.568395026996638</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.177491658948511</v>
       </c>
       <c r="E102">
-        <v>-48.09990198383451</v>
+        <v>-49.75699742051331</v>
       </c>
       <c r="F102">
-        <v>-5.5761909389907</v>
+        <v>-6.086894353429845</v>
       </c>
       <c r="G102">
-        <v>-5.222194727227354</v>
+        <v>-5.673292972953985</v>
       </c>
     </row>
   </sheetData>
